--- a/AutomationCourse/src/test/resources/TestData.xlsx
+++ b/AutomationCourse/src/test/resources/TestData.xlsx
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
   <si>
     <t>secret_sauce</t>
   </si>
   <si>
     <t>standard_user</t>
+  </si>
+  <si>
+    <t>standard_user1</t>
+  </si>
+  <si>
+    <t>Sneha</t>
   </si>
 </sst>
 </file>
@@ -368,11 +374,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -386,6 +392,25 @@
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
